--- a/data/sample_clients.xlsx
+++ b/data/sample_clients.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clients" sheetId="1" r:id="R58e3eb6848c948a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clients" sheetId="1" r:id="Rf5c67368a8784d90"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -221,27 +221,24 @@
         <x:v>sales_rep</x:v>
       </x:c>
       <x:c r="D1" s="3" t="str">
-        <x:v>lat</x:v>
+        <x:v>gps</x:v>
       </x:c>
       <x:c r="E1" s="3" t="str">
-        <x:v>lon</x:v>
+        <x:v>visit_frequency</x:v>
       </x:c>
       <x:c r="F1" s="3" t="str">
-        <x:v>visit_frequency</x:v>
+        <x:v>fixed_weekday</x:v>
       </x:c>
       <x:c r="G1" s="3" t="str">
-        <x:v>fixed_weekday</x:v>
+        <x:v>forbidden_weekdays</x:v>
       </x:c>
       <x:c r="H1" s="3" t="str">
-        <x:v>forbidden_weekdays</x:v>
+        <x:v>preferred_weekdays</x:v>
       </x:c>
       <x:c r="I1" s="3" t="str">
-        <x:v>preferred_weekdays</x:v>
+        <x:v>cluster_manual</x:v>
       </x:c>
       <x:c r="J1" s="3" t="str">
-        <x:v>cluster_manual</x:v>
-      </x:c>
-      <x:c r="K1" s="3" t="str">
         <x:v>notes</x:v>
       </x:c>
     </x:row>
@@ -255,22 +252,19 @@
       <x:c r="C2" s="4" t="str">
         <x:v>Rep A</x:v>
       </x:c>
-      <x:c r="D2" s="4" t="n">
-        <x:v>42.6509</x:v>
+      <x:c r="D2" s="4" t="str">
+        <x:v>42.650900,23.379600</x:v>
       </x:c>
       <x:c r="E2" s="4" t="n">
-        <x:v>23.3796</x:v>
-      </x:c>
-      <x:c r="F2" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F2" s="4" t="str"/>
       <x:c r="G2" s="4" t="str"/>
       <x:c r="H2" s="4" t="str"/>
-      <x:c r="I2" s="4" t="str"/>
+      <x:c r="I2" s="4" t="str">
+        <x:v>Mladost</x:v>
+      </x:c>
       <x:c r="J2" s="4" t="str">
-        <x:v>Mladost</x:v>
-      </x:c>
-      <x:c r="K2" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -284,22 +278,19 @@
       <x:c r="C3" s="4" t="str">
         <x:v>Rep A</x:v>
       </x:c>
-      <x:c r="D3" s="4" t="n">
-        <x:v>42.6725</x:v>
+      <x:c r="D3" s="4" t="str">
+        <x:v>42.672500,23.319600</x:v>
       </x:c>
       <x:c r="E3" s="4" t="n">
-        <x:v>23.3196</x:v>
-      </x:c>
-      <x:c r="F3" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F3" s="4" t="str"/>
       <x:c r="G3" s="4" t="str"/>
       <x:c r="H3" s="4" t="str"/>
-      <x:c r="I3" s="4" t="str"/>
+      <x:c r="I3" s="4" t="str">
+        <x:v>Lozenets</x:v>
+      </x:c>
       <x:c r="J3" s="4" t="str">
-        <x:v>Lozenets</x:v>
-      </x:c>
-      <x:c r="K3" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -313,22 +304,19 @@
       <x:c r="C4" s="4" t="str">
         <x:v>Rep A</x:v>
       </x:c>
-      <x:c r="D4" s="4" t="n">
-        <x:v>42.7169</x:v>
+      <x:c r="D4" s="4" t="str">
+        <x:v>42.716900,23.256300</x:v>
       </x:c>
       <x:c r="E4" s="4" t="n">
-        <x:v>23.2563</x:v>
-      </x:c>
-      <x:c r="F4" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F4" s="4" t="str"/>
       <x:c r="G4" s="4" t="str"/>
       <x:c r="H4" s="4" t="str"/>
-      <x:c r="I4" s="4" t="str"/>
+      <x:c r="I4" s="4" t="str">
+        <x:v>Lyulin</x:v>
+      </x:c>
       <x:c r="J4" s="4" t="str">
-        <x:v>Lyulin</x:v>
-      </x:c>
-      <x:c r="K4" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -342,22 +330,19 @@
       <x:c r="C5" s="4" t="str">
         <x:v>Rep A</x:v>
       </x:c>
-      <x:c r="D5" s="4" t="n">
-        <x:v>42.7379</x:v>
+      <x:c r="D5" s="4" t="str">
+        <x:v>42.737900,23.304700</x:v>
       </x:c>
       <x:c r="E5" s="4" t="n">
-        <x:v>23.3047</x:v>
-      </x:c>
-      <x:c r="F5" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F5" s="4" t="str"/>
       <x:c r="G5" s="4" t="str"/>
       <x:c r="H5" s="4" t="str"/>
-      <x:c r="I5" s="4" t="str"/>
+      <x:c r="I5" s="4" t="str">
+        <x:v>Nadezhda</x:v>
+      </x:c>
       <x:c r="J5" s="4" t="str">
-        <x:v>Nadezhda</x:v>
-      </x:c>
-      <x:c r="K5" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -371,22 +356,19 @@
       <x:c r="C6" s="4" t="str">
         <x:v>Rep A</x:v>
       </x:c>
-      <x:c r="D6" s="4" t="n">
-        <x:v>42.6521</x:v>
+      <x:c r="D6" s="4" t="str">
+        <x:v>42.652100,23.380700</x:v>
       </x:c>
       <x:c r="E6" s="4" t="n">
-        <x:v>23.3807</x:v>
-      </x:c>
-      <x:c r="F6" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F6" s="4" t="str"/>
       <x:c r="G6" s="4" t="str"/>
       <x:c r="H6" s="4" t="str"/>
-      <x:c r="I6" s="4" t="str"/>
+      <x:c r="I6" s="4" t="str">
+        <x:v>Mladost</x:v>
+      </x:c>
       <x:c r="J6" s="4" t="str">
-        <x:v>Mladost</x:v>
-      </x:c>
-      <x:c r="K6" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -400,22 +382,19 @@
       <x:c r="C7" s="4" t="str">
         <x:v>Rep A</x:v>
       </x:c>
-      <x:c r="D7" s="4" t="n">
-        <x:v>42.6737</x:v>
+      <x:c r="D7" s="4" t="str">
+        <x:v>42.673700,23.319800</x:v>
       </x:c>
       <x:c r="E7" s="4" t="n">
-        <x:v>23.3198</x:v>
-      </x:c>
-      <x:c r="F7" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F7" s="4" t="str"/>
       <x:c r="G7" s="4" t="str"/>
       <x:c r="H7" s="4" t="str"/>
-      <x:c r="I7" s="4" t="str"/>
+      <x:c r="I7" s="4" t="str">
+        <x:v>Lozenets</x:v>
+      </x:c>
       <x:c r="J7" s="4" t="str">
-        <x:v>Lozenets</x:v>
-      </x:c>
-      <x:c r="K7" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -429,22 +408,19 @@
       <x:c r="C8" s="4" t="str">
         <x:v>Rep A</x:v>
       </x:c>
-      <x:c r="D8" s="4" t="n">
-        <x:v>42.7181</x:v>
+      <x:c r="D8" s="4" t="str">
+        <x:v>42.718100,23.258300</x:v>
       </x:c>
       <x:c r="E8" s="4" t="n">
-        <x:v>23.2583</x:v>
-      </x:c>
-      <x:c r="F8" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F8" s="4" t="str"/>
       <x:c r="G8" s="4" t="str"/>
       <x:c r="H8" s="4" t="str"/>
-      <x:c r="I8" s="4" t="str"/>
+      <x:c r="I8" s="4" t="str">
+        <x:v>Lyulin</x:v>
+      </x:c>
       <x:c r="J8" s="4" t="str">
-        <x:v>Lyulin</x:v>
-      </x:c>
-      <x:c r="K8" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -458,22 +434,19 @@
       <x:c r="C9" s="4" t="str">
         <x:v>Rep A</x:v>
       </x:c>
-      <x:c r="D9" s="4" t="n">
-        <x:v>42.7391</x:v>
+      <x:c r="D9" s="4" t="str">
+        <x:v>42.739100,23.305800</x:v>
       </x:c>
       <x:c r="E9" s="4" t="n">
-        <x:v>23.3058</x:v>
-      </x:c>
-      <x:c r="F9" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F9" s="4" t="str"/>
       <x:c r="G9" s="4" t="str"/>
       <x:c r="H9" s="4" t="str"/>
-      <x:c r="I9" s="4" t="str"/>
+      <x:c r="I9" s="4" t="str">
+        <x:v>Nadezhda</x:v>
+      </x:c>
       <x:c r="J9" s="4" t="str">
-        <x:v>Nadezhda</x:v>
-      </x:c>
-      <x:c r="K9" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -487,22 +460,19 @@
       <x:c r="C10" s="4" t="str">
         <x:v>Rep A</x:v>
       </x:c>
-      <x:c r="D10" s="4" t="n">
-        <x:v>42.6533</x:v>
+      <x:c r="D10" s="4" t="str">
+        <x:v>42.653300,23.380900</x:v>
       </x:c>
       <x:c r="E10" s="4" t="n">
-        <x:v>23.3809</x:v>
-      </x:c>
-      <x:c r="F10" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F10" s="4" t="str"/>
       <x:c r="G10" s="4" t="str"/>
       <x:c r="H10" s="4" t="str"/>
-      <x:c r="I10" s="4" t="str"/>
+      <x:c r="I10" s="4" t="str">
+        <x:v>Mladost</x:v>
+      </x:c>
       <x:c r="J10" s="4" t="str">
-        <x:v>Mladost</x:v>
-      </x:c>
-      <x:c r="K10" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -516,22 +486,19 @@
       <x:c r="C11" s="4" t="str">
         <x:v>Rep A</x:v>
       </x:c>
-      <x:c r="D11" s="4" t="n">
-        <x:v>42.6749</x:v>
+      <x:c r="D11" s="4" t="str">
+        <x:v>42.674900,23.321800</x:v>
       </x:c>
       <x:c r="E11" s="4" t="n">
-        <x:v>23.3218</x:v>
-      </x:c>
-      <x:c r="F11" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F11" s="4" t="str"/>
       <x:c r="G11" s="4" t="str"/>
       <x:c r="H11" s="4" t="str"/>
-      <x:c r="I11" s="4" t="str"/>
+      <x:c r="I11" s="4" t="str">
+        <x:v>Lozenets</x:v>
+      </x:c>
       <x:c r="J11" s="4" t="str">
-        <x:v>Lozenets</x:v>
-      </x:c>
-      <x:c r="K11" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -545,22 +512,19 @@
       <x:c r="C12" s="4" t="str">
         <x:v>Rep A</x:v>
       </x:c>
-      <x:c r="D12" s="4" t="n">
-        <x:v>42.7193</x:v>
+      <x:c r="D12" s="4" t="str">
+        <x:v>42.719300,23.259400</x:v>
       </x:c>
       <x:c r="E12" s="4" t="n">
-        <x:v>23.2594</x:v>
-      </x:c>
-      <x:c r="F12" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F12" s="4" t="str"/>
       <x:c r="G12" s="4" t="str"/>
       <x:c r="H12" s="4" t="str"/>
-      <x:c r="I12" s="4" t="str"/>
+      <x:c r="I12" s="4" t="str">
+        <x:v>Lyulin</x:v>
+      </x:c>
       <x:c r="J12" s="4" t="str">
-        <x:v>Lyulin</x:v>
-      </x:c>
-      <x:c r="K12" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -574,22 +538,19 @@
       <x:c r="C13" s="4" t="str">
         <x:v>Rep A</x:v>
       </x:c>
-      <x:c r="D13" s="4" t="n">
-        <x:v>42.7403</x:v>
+      <x:c r="D13" s="4" t="str">
+        <x:v>42.740300,23.306000</x:v>
       </x:c>
       <x:c r="E13" s="4" t="n">
-        <x:v>23.306</x:v>
-      </x:c>
-      <x:c r="F13" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F13" s="4" t="str"/>
       <x:c r="G13" s="4" t="str"/>
       <x:c r="H13" s="4" t="str"/>
-      <x:c r="I13" s="4" t="str"/>
+      <x:c r="I13" s="4" t="str">
+        <x:v>Nadezhda</x:v>
+      </x:c>
       <x:c r="J13" s="4" t="str">
-        <x:v>Nadezhda</x:v>
-      </x:c>
-      <x:c r="K13" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -603,22 +564,19 @@
       <x:c r="C14" s="4" t="str">
         <x:v>Rep A</x:v>
       </x:c>
-      <x:c r="D14" s="4" t="n">
-        <x:v>42.6545</x:v>
+      <x:c r="D14" s="4" t="str">
+        <x:v>42.654500,23.382900</x:v>
       </x:c>
       <x:c r="E14" s="4" t="n">
-        <x:v>23.3829</x:v>
-      </x:c>
-      <x:c r="F14" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F14" s="4" t="str"/>
       <x:c r="G14" s="4" t="str"/>
       <x:c r="H14" s="4" t="str"/>
-      <x:c r="I14" s="4" t="str"/>
+      <x:c r="I14" s="4" t="str">
+        <x:v>Mladost</x:v>
+      </x:c>
       <x:c r="J14" s="4" t="str">
-        <x:v>Mladost</x:v>
-      </x:c>
-      <x:c r="K14" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -632,22 +590,19 @@
       <x:c r="C15" s="4" t="str">
         <x:v>Rep A</x:v>
       </x:c>
-      <x:c r="D15" s="4" t="n">
-        <x:v>42.6761</x:v>
+      <x:c r="D15" s="4" t="str">
+        <x:v>42.676100,23.322900</x:v>
       </x:c>
       <x:c r="E15" s="4" t="n">
-        <x:v>23.3229</x:v>
-      </x:c>
-      <x:c r="F15" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F15" s="4" t="str"/>
       <x:c r="G15" s="4" t="str"/>
       <x:c r="H15" s="4" t="str"/>
-      <x:c r="I15" s="4" t="str"/>
+      <x:c r="I15" s="4" t="str">
+        <x:v>Lozenets</x:v>
+      </x:c>
       <x:c r="J15" s="4" t="str">
-        <x:v>Lozenets</x:v>
-      </x:c>
-      <x:c r="K15" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -661,22 +616,19 @@
       <x:c r="C16" s="4" t="str">
         <x:v>Rep A</x:v>
       </x:c>
-      <x:c r="D16" s="4" t="n">
-        <x:v>42.7205</x:v>
+      <x:c r="D16" s="4" t="str">
+        <x:v>42.720500,23.259600</x:v>
       </x:c>
       <x:c r="E16" s="4" t="n">
-        <x:v>23.2596</x:v>
-      </x:c>
-      <x:c r="F16" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F16" s="4" t="str"/>
       <x:c r="G16" s="4" t="str"/>
       <x:c r="H16" s="4" t="str"/>
-      <x:c r="I16" s="4" t="str"/>
+      <x:c r="I16" s="4" t="str">
+        <x:v>Lyulin</x:v>
+      </x:c>
       <x:c r="J16" s="4" t="str">
-        <x:v>Lyulin</x:v>
-      </x:c>
-      <x:c r="K16" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -690,22 +642,19 @@
       <x:c r="C17" s="4" t="str">
         <x:v>Rep A</x:v>
       </x:c>
-      <x:c r="D17" s="4" t="n">
-        <x:v>42.7415</x:v>
+      <x:c r="D17" s="4" t="str">
+        <x:v>42.741500,23.308000</x:v>
       </x:c>
       <x:c r="E17" s="4" t="n">
-        <x:v>23.308</x:v>
-      </x:c>
-      <x:c r="F17" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F17" s="4" t="str"/>
       <x:c r="G17" s="4" t="str"/>
       <x:c r="H17" s="4" t="str"/>
-      <x:c r="I17" s="4" t="str"/>
+      <x:c r="I17" s="4" t="str">
+        <x:v>Nadezhda</x:v>
+      </x:c>
       <x:c r="J17" s="4" t="str">
-        <x:v>Nadezhda</x:v>
-      </x:c>
-      <x:c r="K17" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -719,22 +668,19 @@
       <x:c r="C18" s="4" t="str">
         <x:v>Rep A</x:v>
       </x:c>
-      <x:c r="D18" s="4" t="n">
-        <x:v>42.6557</x:v>
+      <x:c r="D18" s="4" t="str">
+        <x:v>42.655700,23.384000</x:v>
       </x:c>
       <x:c r="E18" s="4" t="n">
-        <x:v>23.384</x:v>
-      </x:c>
-      <x:c r="F18" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F18" s="4" t="str"/>
       <x:c r="G18" s="4" t="str"/>
       <x:c r="H18" s="4" t="str"/>
-      <x:c r="I18" s="4" t="str"/>
+      <x:c r="I18" s="4" t="str">
+        <x:v>Mladost</x:v>
+      </x:c>
       <x:c r="J18" s="4" t="str">
-        <x:v>Mladost</x:v>
-      </x:c>
-      <x:c r="K18" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -748,22 +694,19 @@
       <x:c r="C19" s="4" t="str">
         <x:v>Rep A</x:v>
       </x:c>
-      <x:c r="D19" s="4" t="n">
-        <x:v>42.6773</x:v>
+      <x:c r="D19" s="4" t="str">
+        <x:v>42.677300,23.323100</x:v>
       </x:c>
       <x:c r="E19" s="4" t="n">
-        <x:v>23.3231</x:v>
-      </x:c>
-      <x:c r="F19" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F19" s="4" t="str"/>
       <x:c r="G19" s="4" t="str"/>
       <x:c r="H19" s="4" t="str"/>
-      <x:c r="I19" s="4" t="str"/>
+      <x:c r="I19" s="4" t="str">
+        <x:v>Lozenets</x:v>
+      </x:c>
       <x:c r="J19" s="4" t="str">
-        <x:v>Lozenets</x:v>
-      </x:c>
-      <x:c r="K19" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -777,22 +720,19 @@
       <x:c r="C20" s="4" t="str">
         <x:v>Rep A</x:v>
       </x:c>
-      <x:c r="D20" s="4" t="n">
-        <x:v>42.7217</x:v>
+      <x:c r="D20" s="4" t="str">
+        <x:v>42.721700,23.261600</x:v>
       </x:c>
       <x:c r="E20" s="4" t="n">
-        <x:v>23.2616</x:v>
-      </x:c>
-      <x:c r="F20" s="4" t="n">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="F20" s="4" t="str"/>
       <x:c r="G20" s="4" t="str"/>
       <x:c r="H20" s="4" t="str"/>
-      <x:c r="I20" s="4" t="str"/>
+      <x:c r="I20" s="4" t="str">
+        <x:v>Lyulin</x:v>
+      </x:c>
       <x:c r="J20" s="4" t="str">
-        <x:v>Lyulin</x:v>
-      </x:c>
-      <x:c r="K20" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -806,22 +746,19 @@
       <x:c r="C21" s="4" t="str">
         <x:v>Rep A</x:v>
       </x:c>
-      <x:c r="D21" s="4" t="n">
-        <x:v>42.7427</x:v>
+      <x:c r="D21" s="4" t="str">
+        <x:v>42.742700,23.309100</x:v>
       </x:c>
       <x:c r="E21" s="4" t="n">
-        <x:v>23.3091</x:v>
-      </x:c>
-      <x:c r="F21" s="4" t="n">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="F21" s="4" t="str"/>
       <x:c r="G21" s="4" t="str"/>
       <x:c r="H21" s="4" t="str"/>
-      <x:c r="I21" s="4" t="str"/>
+      <x:c r="I21" s="4" t="str">
+        <x:v>Nadezhda</x:v>
+      </x:c>
       <x:c r="J21" s="4" t="str">
-        <x:v>Nadezhda</x:v>
-      </x:c>
-      <x:c r="K21" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -835,22 +772,19 @@
       <x:c r="C22" s="4" t="str">
         <x:v>Rep B</x:v>
       </x:c>
-      <x:c r="D22" s="4" t="n">
-        <x:v>42.6569</x:v>
+      <x:c r="D22" s="4" t="str">
+        <x:v>42.656900,23.383800</x:v>
       </x:c>
       <x:c r="E22" s="4" t="n">
-        <x:v>23.3838</x:v>
-      </x:c>
-      <x:c r="F22" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F22" s="4" t="str"/>
       <x:c r="G22" s="4" t="str"/>
       <x:c r="H22" s="4" t="str"/>
-      <x:c r="I22" s="4" t="str"/>
+      <x:c r="I22" s="4" t="str">
+        <x:v>Mladost</x:v>
+      </x:c>
       <x:c r="J22" s="4" t="str">
-        <x:v>Mladost</x:v>
-      </x:c>
-      <x:c r="K22" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -864,22 +798,19 @@
       <x:c r="C23" s="4" t="str">
         <x:v>Rep B</x:v>
       </x:c>
-      <x:c r="D23" s="4" t="n">
-        <x:v>42.6785</x:v>
+      <x:c r="D23" s="4" t="str">
+        <x:v>42.678500,23.323800</x:v>
       </x:c>
       <x:c r="E23" s="4" t="n">
-        <x:v>23.3238</x:v>
-      </x:c>
-      <x:c r="F23" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F23" s="4" t="str"/>
       <x:c r="G23" s="4" t="str"/>
       <x:c r="H23" s="4" t="str"/>
-      <x:c r="I23" s="4" t="str"/>
+      <x:c r="I23" s="4" t="str">
+        <x:v>Lozenets</x:v>
+      </x:c>
       <x:c r="J23" s="4" t="str">
-        <x:v>Lozenets</x:v>
-      </x:c>
-      <x:c r="K23" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -893,22 +824,19 @@
       <x:c r="C24" s="4" t="str">
         <x:v>Rep B</x:v>
       </x:c>
-      <x:c r="D24" s="4" t="n">
-        <x:v>42.7229</x:v>
+      <x:c r="D24" s="4" t="str">
+        <x:v>42.722900,23.260500</x:v>
       </x:c>
       <x:c r="E24" s="4" t="n">
-        <x:v>23.2605</x:v>
-      </x:c>
-      <x:c r="F24" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F24" s="4" t="str"/>
       <x:c r="G24" s="4" t="str"/>
       <x:c r="H24" s="4" t="str"/>
-      <x:c r="I24" s="4" t="str"/>
+      <x:c r="I24" s="4" t="str">
+        <x:v>Lyulin</x:v>
+      </x:c>
       <x:c r="J24" s="4" t="str">
-        <x:v>Lyulin</x:v>
-      </x:c>
-      <x:c r="K24" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -922,22 +850,19 @@
       <x:c r="C25" s="4" t="str">
         <x:v>Rep B</x:v>
       </x:c>
-      <x:c r="D25" s="4" t="n">
-        <x:v>42.7439</x:v>
+      <x:c r="D25" s="4" t="str">
+        <x:v>42.743900,23.308900</x:v>
       </x:c>
       <x:c r="E25" s="4" t="n">
-        <x:v>23.3089</x:v>
-      </x:c>
-      <x:c r="F25" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F25" s="4" t="str"/>
       <x:c r="G25" s="4" t="str"/>
       <x:c r="H25" s="4" t="str"/>
-      <x:c r="I25" s="4" t="str"/>
+      <x:c r="I25" s="4" t="str">
+        <x:v>Nadezhda</x:v>
+      </x:c>
       <x:c r="J25" s="4" t="str">
-        <x:v>Nadezhda</x:v>
-      </x:c>
-      <x:c r="K25" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -951,22 +876,19 @@
       <x:c r="C26" s="4" t="str">
         <x:v>Rep B</x:v>
       </x:c>
-      <x:c r="D26" s="4" t="n">
-        <x:v>42.6581</x:v>
+      <x:c r="D26" s="4" t="str">
+        <x:v>42.658100,23.384900</x:v>
       </x:c>
       <x:c r="E26" s="4" t="n">
-        <x:v>23.3849</x:v>
-      </x:c>
-      <x:c r="F26" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F26" s="4" t="str"/>
       <x:c r="G26" s="4" t="str"/>
       <x:c r="H26" s="4" t="str"/>
-      <x:c r="I26" s="4" t="str"/>
+      <x:c r="I26" s="4" t="str">
+        <x:v>Mladost</x:v>
+      </x:c>
       <x:c r="J26" s="4" t="str">
-        <x:v>Mladost</x:v>
-      </x:c>
-      <x:c r="K26" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -980,22 +902,19 @@
       <x:c r="C27" s="4" t="str">
         <x:v>Rep B</x:v>
       </x:c>
-      <x:c r="D27" s="4" t="n">
-        <x:v>42.6797</x:v>
+      <x:c r="D27" s="4" t="str">
+        <x:v>42.679700,23.324000</x:v>
       </x:c>
       <x:c r="E27" s="4" t="n">
-        <x:v>23.324</x:v>
-      </x:c>
-      <x:c r="F27" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F27" s="4" t="str"/>
       <x:c r="G27" s="4" t="str"/>
       <x:c r="H27" s="4" t="str"/>
-      <x:c r="I27" s="4" t="str"/>
+      <x:c r="I27" s="4" t="str">
+        <x:v>Lozenets</x:v>
+      </x:c>
       <x:c r="J27" s="4" t="str">
-        <x:v>Lozenets</x:v>
-      </x:c>
-      <x:c r="K27" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -1009,22 +928,19 @@
       <x:c r="C28" s="4" t="str">
         <x:v>Rep B</x:v>
       </x:c>
-      <x:c r="D28" s="4" t="n">
-        <x:v>42.7241</x:v>
+      <x:c r="D28" s="4" t="str">
+        <x:v>42.724100,23.262500</x:v>
       </x:c>
       <x:c r="E28" s="4" t="n">
-        <x:v>23.2625</x:v>
-      </x:c>
-      <x:c r="F28" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F28" s="4" t="str"/>
       <x:c r="G28" s="4" t="str"/>
       <x:c r="H28" s="4" t="str"/>
-      <x:c r="I28" s="4" t="str"/>
+      <x:c r="I28" s="4" t="str">
+        <x:v>Lyulin</x:v>
+      </x:c>
       <x:c r="J28" s="4" t="str">
-        <x:v>Lyulin</x:v>
-      </x:c>
-      <x:c r="K28" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -1038,22 +954,19 @@
       <x:c r="C29" s="4" t="str">
         <x:v>Rep B</x:v>
       </x:c>
-      <x:c r="D29" s="4" t="n">
-        <x:v>42.7451</x:v>
+      <x:c r="D29" s="4" t="str">
+        <x:v>42.745100,23.310000</x:v>
       </x:c>
       <x:c r="E29" s="4" t="n">
-        <x:v>23.31</x:v>
-      </x:c>
-      <x:c r="F29" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F29" s="4" t="str"/>
       <x:c r="G29" s="4" t="str"/>
       <x:c r="H29" s="4" t="str"/>
-      <x:c r="I29" s="4" t="str"/>
+      <x:c r="I29" s="4" t="str">
+        <x:v>Nadezhda</x:v>
+      </x:c>
       <x:c r="J29" s="4" t="str">
-        <x:v>Nadezhda</x:v>
-      </x:c>
-      <x:c r="K29" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -1067,22 +980,19 @@
       <x:c r="C30" s="4" t="str">
         <x:v>Rep B</x:v>
       </x:c>
-      <x:c r="D30" s="4" t="n">
-        <x:v>42.6593</x:v>
+      <x:c r="D30" s="4" t="str">
+        <x:v>42.659300,23.385100</x:v>
       </x:c>
       <x:c r="E30" s="4" t="n">
-        <x:v>23.3851</x:v>
-      </x:c>
-      <x:c r="F30" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F30" s="4" t="str"/>
       <x:c r="G30" s="4" t="str"/>
       <x:c r="H30" s="4" t="str"/>
-      <x:c r="I30" s="4" t="str"/>
+      <x:c r="I30" s="4" t="str">
+        <x:v>Mladost</x:v>
+      </x:c>
       <x:c r="J30" s="4" t="str">
-        <x:v>Mladost</x:v>
-      </x:c>
-      <x:c r="K30" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -1096,22 +1006,19 @@
       <x:c r="C31" s="4" t="str">
         <x:v>Rep B</x:v>
       </x:c>
-      <x:c r="D31" s="4" t="n">
-        <x:v>42.6809</x:v>
+      <x:c r="D31" s="4" t="str">
+        <x:v>42.680900,23.326000</x:v>
       </x:c>
       <x:c r="E31" s="4" t="n">
-        <x:v>23.326</x:v>
-      </x:c>
-      <x:c r="F31" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F31" s="4" t="str"/>
       <x:c r="G31" s="4" t="str"/>
       <x:c r="H31" s="4" t="str"/>
-      <x:c r="I31" s="4" t="str"/>
+      <x:c r="I31" s="4" t="str">
+        <x:v>Lozenets</x:v>
+      </x:c>
       <x:c r="J31" s="4" t="str">
-        <x:v>Lozenets</x:v>
-      </x:c>
-      <x:c r="K31" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -1125,22 +1032,19 @@
       <x:c r="C32" s="4" t="str">
         <x:v>Rep B</x:v>
       </x:c>
-      <x:c r="D32" s="4" t="n">
-        <x:v>42.7253</x:v>
+      <x:c r="D32" s="4" t="str">
+        <x:v>42.725300,23.263600</x:v>
       </x:c>
       <x:c r="E32" s="4" t="n">
-        <x:v>23.2636</x:v>
-      </x:c>
-      <x:c r="F32" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F32" s="4" t="str"/>
       <x:c r="G32" s="4" t="str"/>
       <x:c r="H32" s="4" t="str"/>
-      <x:c r="I32" s="4" t="str"/>
+      <x:c r="I32" s="4" t="str">
+        <x:v>Lyulin</x:v>
+      </x:c>
       <x:c r="J32" s="4" t="str">
-        <x:v>Lyulin</x:v>
-      </x:c>
-      <x:c r="K32" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -1154,22 +1058,19 @@
       <x:c r="C33" s="4" t="str">
         <x:v>Rep B</x:v>
       </x:c>
-      <x:c r="D33" s="4" t="n">
-        <x:v>42.7463</x:v>
+      <x:c r="D33" s="4" t="str">
+        <x:v>42.746300,23.310200</x:v>
       </x:c>
       <x:c r="E33" s="4" t="n">
-        <x:v>23.3102</x:v>
-      </x:c>
-      <x:c r="F33" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F33" s="4" t="str"/>
       <x:c r="G33" s="4" t="str"/>
       <x:c r="H33" s="4" t="str"/>
-      <x:c r="I33" s="4" t="str"/>
+      <x:c r="I33" s="4" t="str">
+        <x:v>Nadezhda</x:v>
+      </x:c>
       <x:c r="J33" s="4" t="str">
-        <x:v>Nadezhda</x:v>
-      </x:c>
-      <x:c r="K33" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -1183,22 +1084,19 @@
       <x:c r="C34" s="4" t="str">
         <x:v>Rep B</x:v>
       </x:c>
-      <x:c r="D34" s="4" t="n">
-        <x:v>42.6605</x:v>
+      <x:c r="D34" s="4" t="str">
+        <x:v>42.660500,23.387100</x:v>
       </x:c>
       <x:c r="E34" s="4" t="n">
-        <x:v>23.3871</x:v>
-      </x:c>
-      <x:c r="F34" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F34" s="4" t="str"/>
       <x:c r="G34" s="4" t="str"/>
       <x:c r="H34" s="4" t="str"/>
-      <x:c r="I34" s="4" t="str"/>
+      <x:c r="I34" s="4" t="str">
+        <x:v>Mladost</x:v>
+      </x:c>
       <x:c r="J34" s="4" t="str">
-        <x:v>Mladost</x:v>
-      </x:c>
-      <x:c r="K34" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -1212,22 +1110,19 @@
       <x:c r="C35" s="4" t="str">
         <x:v>Rep B</x:v>
       </x:c>
-      <x:c r="D35" s="4" t="n">
-        <x:v>42.6821</x:v>
+      <x:c r="D35" s="4" t="str">
+        <x:v>42.682100,23.327100</x:v>
       </x:c>
       <x:c r="E35" s="4" t="n">
-        <x:v>23.3271</x:v>
-      </x:c>
-      <x:c r="F35" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F35" s="4" t="str"/>
       <x:c r="G35" s="4" t="str"/>
       <x:c r="H35" s="4" t="str"/>
-      <x:c r="I35" s="4" t="str"/>
+      <x:c r="I35" s="4" t="str">
+        <x:v>Lozenets</x:v>
+      </x:c>
       <x:c r="J35" s="4" t="str">
-        <x:v>Lozenets</x:v>
-      </x:c>
-      <x:c r="K35" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -1241,22 +1136,19 @@
       <x:c r="C36" s="4" t="str">
         <x:v>Rep B</x:v>
       </x:c>
-      <x:c r="D36" s="4" t="n">
-        <x:v>42.7265</x:v>
+      <x:c r="D36" s="4" t="str">
+        <x:v>42.726500,23.263800</x:v>
       </x:c>
       <x:c r="E36" s="4" t="n">
-        <x:v>23.2638</x:v>
-      </x:c>
-      <x:c r="F36" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F36" s="4" t="str"/>
       <x:c r="G36" s="4" t="str"/>
       <x:c r="H36" s="4" t="str"/>
-      <x:c r="I36" s="4" t="str"/>
+      <x:c r="I36" s="4" t="str">
+        <x:v>Lyulin</x:v>
+      </x:c>
       <x:c r="J36" s="4" t="str">
-        <x:v>Lyulin</x:v>
-      </x:c>
-      <x:c r="K36" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -1270,22 +1162,19 @@
       <x:c r="C37" s="4" t="str">
         <x:v>Rep B</x:v>
       </x:c>
-      <x:c r="D37" s="4" t="n">
-        <x:v>42.7475</x:v>
+      <x:c r="D37" s="4" t="str">
+        <x:v>42.747500,23.312200</x:v>
       </x:c>
       <x:c r="E37" s="4" t="n">
-        <x:v>23.3122</x:v>
-      </x:c>
-      <x:c r="F37" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F37" s="4" t="str"/>
       <x:c r="G37" s="4" t="str"/>
       <x:c r="H37" s="4" t="str"/>
-      <x:c r="I37" s="4" t="str"/>
+      <x:c r="I37" s="4" t="str">
+        <x:v>Nadezhda</x:v>
+      </x:c>
       <x:c r="J37" s="4" t="str">
-        <x:v>Nadezhda</x:v>
-      </x:c>
-      <x:c r="K37" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -1299,22 +1188,19 @@
       <x:c r="C38" s="4" t="str">
         <x:v>Rep B</x:v>
       </x:c>
-      <x:c r="D38" s="4" t="n">
-        <x:v>42.6617</x:v>
+      <x:c r="D38" s="4" t="str">
+        <x:v>42.661700,23.388200</x:v>
       </x:c>
       <x:c r="E38" s="4" t="n">
-        <x:v>23.3882</x:v>
-      </x:c>
-      <x:c r="F38" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F38" s="4" t="str"/>
       <x:c r="G38" s="4" t="str"/>
       <x:c r="H38" s="4" t="str"/>
-      <x:c r="I38" s="4" t="str"/>
+      <x:c r="I38" s="4" t="str">
+        <x:v>Mladost</x:v>
+      </x:c>
       <x:c r="J38" s="4" t="str">
-        <x:v>Mladost</x:v>
-      </x:c>
-      <x:c r="K38" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -1328,22 +1214,19 @@
       <x:c r="C39" s="4" t="str">
         <x:v>Rep B</x:v>
       </x:c>
-      <x:c r="D39" s="4" t="n">
-        <x:v>42.6833</x:v>
+      <x:c r="D39" s="4" t="str">
+        <x:v>42.683300,23.327300</x:v>
       </x:c>
       <x:c r="E39" s="4" t="n">
-        <x:v>23.3273</x:v>
-      </x:c>
-      <x:c r="F39" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F39" s="4" t="str"/>
       <x:c r="G39" s="4" t="str"/>
       <x:c r="H39" s="4" t="str"/>
-      <x:c r="I39" s="4" t="str"/>
+      <x:c r="I39" s="4" t="str">
+        <x:v>Lozenets</x:v>
+      </x:c>
       <x:c r="J39" s="4" t="str">
-        <x:v>Lozenets</x:v>
-      </x:c>
-      <x:c r="K39" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -1357,22 +1240,19 @@
       <x:c r="C40" s="4" t="str">
         <x:v>Rep B</x:v>
       </x:c>
-      <x:c r="D40" s="4" t="n">
-        <x:v>42.7277</x:v>
+      <x:c r="D40" s="4" t="str">
+        <x:v>42.727700,23.265800</x:v>
       </x:c>
       <x:c r="E40" s="4" t="n">
-        <x:v>23.2658</x:v>
-      </x:c>
-      <x:c r="F40" s="4" t="n">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="F40" s="4" t="str"/>
       <x:c r="G40" s="4" t="str"/>
       <x:c r="H40" s="4" t="str"/>
-      <x:c r="I40" s="4" t="str"/>
+      <x:c r="I40" s="4" t="str">
+        <x:v>Lyulin</x:v>
+      </x:c>
       <x:c r="J40" s="4" t="str">
-        <x:v>Lyulin</x:v>
-      </x:c>
-      <x:c r="K40" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
@@ -1386,22 +1266,19 @@
       <x:c r="C41" s="4" t="str">
         <x:v>Rep B</x:v>
       </x:c>
-      <x:c r="D41" s="4" t="n">
-        <x:v>42.7487</x:v>
+      <x:c r="D41" s="4" t="str">
+        <x:v>42.748700,23.313300</x:v>
       </x:c>
       <x:c r="E41" s="4" t="n">
-        <x:v>23.3133</x:v>
-      </x:c>
-      <x:c r="F41" s="4" t="n">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="F41" s="4" t="str"/>
       <x:c r="G41" s="4" t="str"/>
       <x:c r="H41" s="4" t="str"/>
-      <x:c r="I41" s="4" t="str"/>
+      <x:c r="I41" s="4" t="str">
+        <x:v>Nadezhda</x:v>
+      </x:c>
       <x:c r="J41" s="4" t="str">
-        <x:v>Nadezhda</x:v>
-      </x:c>
-      <x:c r="K41" s="4" t="str">
         <x:v>Smoke-test sample row</x:v>
       </x:c>
     </x:row>
